--- a/donnees3.xlsx
+++ b/donnees3.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="entrainement8" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="entrainement10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="entrainement13" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="entrainement14" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -352,6 +354,232 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Graphe de l'évolution des scores</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'entrainement13'!$A$2:$A$101</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'entrainement13'!$B$1:$B$101</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Episode</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Score</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Graphe de l'évolution des scores</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'entrainement14'!$A$2:$A$47</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'entrainement14'!$B$1:$B$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Episode</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Score</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -380,6 +608,60 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2354,4 +2636,1226 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>300</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>400</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>600</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>700</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>800</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>900</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3300</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3900</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4200</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4300</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4400</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5400</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5500</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5600</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5700</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5800</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5900</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6100</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6200</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6300</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6400</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6500</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6600</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6700</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6800</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6900</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7000</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7100</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7200</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7300</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7400</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7500</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>7600</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7700</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7800</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7900</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8000</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8100</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8200</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8300</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8400</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8500</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8600</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8700</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8800</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8900</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9000</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>9100</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9200</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9300</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>9400</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9500</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9600</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9700</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9800</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9900</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.092</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17000</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18000</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19000</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21000</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22000</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23000</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24000</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.064</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26000</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28000</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29000</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30000</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31000</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32000</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34000</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35000</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36000</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.089</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37000</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38000</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39000</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40000</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41000</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42000</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43000</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45000</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.079</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>